--- a/sheets/대금율보/검수/부산 갈메기.xlsx
+++ b/sheets/대금율보/검수/부산 갈메기.xlsx
@@ -3946,11 +3946,7 @@
           <t xml:space="preserve">꽃처</t>
         </is>
       </c>
-      <c r="J4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J4" s="21"/>
       <c r="K4" s="25"/>
       <c r="L4" s="21" t="inlineStr">
         <is>
@@ -4341,11 +4337,7 @@
           <t xml:space="preserve">나는</t>
         </is>
       </c>
-      <c r="F12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F12" s="21"/>
       <c r="G12" s="25"/>
       <c r="H12" s="21" t="inlineStr">
         <is>
@@ -4361,8 +4353,7 @@
       <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳淋
-汰
-‹</t>
+汰</t>
         </is>
       </c>
       <c r="K12" s="25"/>

--- a/sheets/대금율보/검수/부산 갈메기.xlsx
+++ b/sheets/대금율보/검수/부산 갈메기.xlsx
@@ -3830,24 +3830,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="15.29" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="15.29" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="15.29" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="15.29" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="15.29" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="15.29" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="81.63" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="91.25" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="M3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="91.25" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="M4" s="25"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="91.25" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="23" t="inlineStr">
         <is>
@@ -4012,7 +4012,7 @@
       </c>
       <c r="M5" s="25"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="91.25" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="23" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
       </c>
       <c r="M6" s="28"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="91.25" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
       </c>
       <c r="M7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="91.25" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
       </c>
       <c r="M8" s="25"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="91.25" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="M9" s="25"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="91.25" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4276,7 +4276,7 @@
       <c r="L10" s="21"/>
       <c r="M10" s="28"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="91.25" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="22"/>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="M11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="91.25" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="25"/>
@@ -4365,7 +4365,7 @@
       </c>
       <c r="M12" s="25"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="91.25" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
       </c>
       <c r="M13" s="25"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="91.25" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="28"/>
@@ -4478,7 +4478,7 @@
       </c>
       <c r="M14" s="28"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="91.25" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
@@ -4532,7 +4532,7 @@
       </c>
       <c r="M15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="91.25" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="25"/>
@@ -4589,7 +4589,7 @@
       </c>
       <c r="M16" s="25"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="91.25" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="25"/>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="M17" s="25"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="91.25" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="28"/>
@@ -4681,6 +4681,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="77"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="49"/>
 </worksheet>
 </file>